--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ConceptMap/VFSourceOfAdmission</t>
+    <t>http://va.gov/fhir/ConceptMap/CMVFSourceOfAdmission</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:56:35+00:00</t>
+    <t>2023-11-09T22:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Source</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VFSourceOfAdmission</t>
+    <t>http://va.gov/fhir/ValueSet/VSVFSourceOfAdmission</t>
   </si>
   <si>
     <t>Display</t>
@@ -105,7 +105,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>undefined</t>
+    <t>http://va.gov/terminology/vistaDefinedElements/45.1-.01</t>
   </si>
   <si>
     <t/>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -45,7 +45,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>http://va.gov/terminology/vistaDefinedElements/45.1-.01</t>
+    <t>http://va.gov/terminology/vistaDefinedTerms/45.1-.01</t>
   </si>
   <si>
     <t/>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="144">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,13 +51,13 @@
     <t>Experimental</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,6 +93,12 @@
     <t>Source</t>
   </si>
   <si>
+    <t>http://va.gov/fhir/ValueSet/VSVFSourceOfAdmission-vista</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
     <t>http://va.gov/fhir/ValueSet/VSVFSourceOfAdmission</t>
   </si>
   <si>
@@ -100,9 +106,6 @@
   </si>
   <si>
     <t>Relationship</t>
-  </si>
-  <si>
-    <t>Target</t>
   </si>
   <si>
     <t>http://va.gov/terminology/vistaDefinedTerms/45.1-.01</t>
@@ -575,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -696,6 +699,14 @@
       </c>
       <c r="B15" t="s" s="2">
         <v>26</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B16" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -713,827 +724,827 @@
         <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="C1" t="s" s="1">
-        <v>28</v>
-      </c>
-      <c r="D1" t="s" s="1">
+      <c r="E1" t="s" s="1">
         <v>29</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>27</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="E2" t="s" s="2">
         <v>32</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="C6" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D6" t="s" s="2">
-        <v>42</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>51</v>
       </c>
-      <c r="B10" t="s" s="2">
-        <v>50</v>
-      </c>
       <c r="C10" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22" s="2"/>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="B53" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="B53" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="C53" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E55" s="2"/>
     </row>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
+    <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="145">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,19 +115,22 @@
     <t/>
   </si>
   <si>
+    <t>http://terminology.hl7.org/CodeSystem/admit-source|4.0.1</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>ALL OTHER NON VA HOSP NOT UNDER VA AUSPICES</t>
+  </si>
+  <si>
+    <t>source-is-narrower-than-target</t>
+  </si>
+  <si>
+    <t>hosp-trans</t>
+  </si>
+  <si>
     <t>http://terminology.hl7.org/CodeSystem/admit-source</t>
-  </si>
-  <si>
-    <t>1K</t>
-  </si>
-  <si>
-    <t>ALL OTHER NON VA HOSP NOT UNDER VA AUSPICES</t>
-  </si>
-  <si>
-    <t>source-is-narrower-than-target</t>
-  </si>
-  <si>
-    <t>hosp-trans</t>
   </si>
   <si>
     <t>4Y</t>
@@ -716,7 +720,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -768,57 +772,116 @@
       </c>
       <c r="E3" s="2"/>
     </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E54"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>30</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>36</v>
@@ -830,70 +893,70 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>36</v>
@@ -905,55 +968,55 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>36</v>
@@ -965,10 +1028,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>36</v>
@@ -980,10 +1043,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>36</v>
@@ -995,55 +1058,55 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>36</v>
@@ -1055,498 +1118,483 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>83</v>
+        <v>37</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D34" t="s" s="2">
         <v>101</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="C34" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D34" t="s" s="2">
-        <v>40</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C54" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E54" s="2"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D55" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E55" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
-    <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="144">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -58,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,7 +114,7 @@
     <t/>
   </si>
   <si>
-    <t>http://terminology.hl7.org/CodeSystem/admit-source|4.0.1</t>
+    <t>http://terminology.hl7.org/CodeSystem/admit-source</t>
   </si>
   <si>
     <t>1K</t>
@@ -128,9 +127,6 @@
   </si>
   <si>
     <t>hosp-trans</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/admit-source</t>
   </si>
   <si>
     <t>4Y</t>
@@ -720,7 +716,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -772,116 +768,57 @@
       </c>
       <c r="E3" s="2"/>
     </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E54"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>25</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>29</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>30</v>
-      </c>
-      <c r="D1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D2" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="C3" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="E3" s="2"/>
-    </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C4" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" t="s" s="2">
         <v>36</v>
@@ -893,70 +830,70 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C8" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>36</v>
@@ -968,55 +905,55 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C13" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s" s="2">
         <v>36</v>
@@ -1028,10 +965,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s" s="2">
         <v>36</v>
@@ -1043,10 +980,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C18" t="s" s="2">
         <v>36</v>
@@ -1058,55 +995,55 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2"/>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2"/>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D21" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C22" t="s" s="2">
         <v>36</v>
@@ -1118,483 +1055,498 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D23" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D24" t="s" s="2">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="E24" s="2"/>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D25" t="s" s="2">
-        <v>37</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D26" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2"/>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C29" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>101</v>
+        <v>40</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C35" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>41</v>
+        <v>100</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C36" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C40" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C43" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C46" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C49" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C51" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C53" t="s" s="2">
         <v>36</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C54" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="E54" s="2"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B55" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="B54" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="D54" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="E54" s="2"/>
+      <c r="C55" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="D55" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="E55" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.354</t>
+    <t>0.66.364</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-19T08:45:12+00:00</t>
+    <t>2024-10-02T18:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/CMVFSourceOfAdmission.xlsx
+++ b/docs/CMVFSourceOfAdmission.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
